--- a/data/output/corpus_run_v7_mobile_500/queries.xlsx
+++ b/data/output/corpus_run_v7_mobile_500/queries.xlsx
@@ -13700,19 +13700,19 @@
         <v>medium</v>
       </c>
       <c r="H350">
+        <v>51</v>
+      </c>
+      <c r="I350">
         <v>0</v>
       </c>
-      <c r="I350">
-        <v>546736</v>
-      </c>
       <c r="J350" t="str">
-        <v/>
+        <v>Create a HIIT workout timer for my phone that counts rounds and tracks work and rest intervals, with a clear display showing the current round number out of the total, a big countdown clock for each interval, and a simple way to set how many rounds I want before I start.</v>
       </c>
       <c r="K350" t="str">
-        <v/>
+        <v>给手机做一个HIIT训练计时器，能记录组数、追踪工作和休息的时间段，显示当前是第几组以及总共多少组，每个时间段有个大的倒计时显示，开始前还能简单地设置要做多少组。</v>
       </c>
       <c r="L350" t="str">
-        <v>[q_scene_035_006] 超时 180000ms</v>
+        <v/>
       </c>
     </row>
     <row r="351">
@@ -13928,19 +13928,19 @@
         <v>medium</v>
       </c>
       <c r="H356">
+        <v>48</v>
+      </c>
+      <c r="I356">
         <v>0</v>
       </c>
-      <c r="I356">
-        <v>546894</v>
-      </c>
       <c r="J356" t="str">
-        <v/>
+        <v>Make a PMS symptom and mood tracker for my phone where I can log each day's physical symptoms and how I'm feeling emotionally, then see a summary that shows which symptoms tend to show up together with certain moods so I can spot my own patterns over time.</v>
       </c>
       <c r="K356" t="str">
-        <v/>
+        <v>做一个手机经期症状和心情追踪应用，我可以每天记录身体症状和情绪感受，然后看一个总结，显示哪些症状容易和什么心情一起出现，这样我就能慢慢看出自己的规律。</v>
       </c>
       <c r="L356" t="str">
-        <v>[q_scene_036_004] 超时 180000ms</v>
+        <v/>
       </c>
     </row>
     <row r="357">
@@ -13966,19 +13966,19 @@
         <v>medium</v>
       </c>
       <c r="H357">
+        <v>55</v>
+      </c>
+      <c r="I357">
         <v>0</v>
       </c>
-      <c r="I357">
-        <v>546974</v>
-      </c>
       <c r="J357" t="str">
-        <v/>
+        <v>A sleep recorder app for my phone where I can tap to log the time I fall asleep and the time I wake up each day, with a running log of all my entries and a simple calculation showing how many hours I slept each night so I can keep track of my sleep routine.</v>
       </c>
       <c r="K357" t="str">
-        <v/>
+        <v>手机睡眠记录应用，我可以点击记录入睡时间和起床时间，有一个运行日志显示所有记录，还能自动算出每晚睡了多少小时，这样我就能跟踪自己的睡眠规律。</v>
       </c>
       <c r="L357" t="str">
-        <v>[q_scene_036_005] 超时 180000ms</v>
+        <v/>
       </c>
     </row>
     <row r="358">
@@ -14004,19 +14004,19 @@
         <v>medium</v>
       </c>
       <c r="H358">
+        <v>45</v>
+      </c>
+      <c r="I358">
         <v>0</v>
       </c>
-      <c r="I358">
-        <v>547156</v>
-      </c>
       <c r="J358" t="str">
-        <v/>
+        <v>Need a sleep quality tracker for my phone that pulls in my sleep score from my wearable and shows it clearly each morning, along with a log of past nights so I can see whether my score is going up or down over the week.</v>
       </c>
       <c r="K358" t="str">
-        <v/>
+        <v>手机睡眠质量追踪器，能从手环同步睡眠评分并每天早上清晰显示，还有过去几晚的日志，这样我能看出这一周的评分是上升还是下降。</v>
       </c>
       <c r="L358" t="str">
-        <v>[q_scene_036_006] 超时 180000ms</v>
+        <v/>
       </c>
     </row>
     <row r="359">
@@ -14080,19 +14080,19 @@
         <v>medium</v>
       </c>
       <c r="H360">
+        <v>49</v>
+      </c>
+      <c r="I360">
         <v>0</v>
       </c>
-      <c r="I360">
-        <v>546871</v>
-      </c>
       <c r="J360" t="str">
-        <v/>
+        <v>Need a pregnancy milestone tracker for my phone that goes week by week through all 40 weeks, showing what's happening with the baby each week and letting me check off milestones like the first ultrasound or hearing the heartbeat so I have a clear record of the whole journey.</v>
       </c>
       <c r="K360" t="str">
-        <v/>
+        <v>手机怀孕里程碑追踪器，按周数从第1周到40周逐周显示宝宝每周的发育情况，我可以勾选一些里程碑事件比如首次超声检查或听到心跳声，这样能清楚地记录整个过程。</v>
       </c>
       <c r="L360" t="str">
-        <v>[q_scene_036_008] 超时 180000ms</v>
+        <v/>
       </c>
     </row>
     <row r="361">
@@ -14118,19 +14118,19 @@
         <v>medium</v>
       </c>
       <c r="H361">
+        <v>45</v>
+      </c>
+      <c r="I361">
         <v>0</v>
       </c>
-      <c r="I361">
-        <v>546967</v>
-      </c>
       <c r="J361" t="str">
-        <v/>
+        <v>Create a daily vitals tracker for my phone that shows today's heart rate, blood pressure, blood oxygen level, and body temperature all in one place, with a spot to enter each reading and a quick look at whether each number is in a normal range.</v>
       </c>
       <c r="K361" t="str">
-        <v/>
+        <v>手机日常生命体征追踪器，把今天的心率、血压、血氧饱和度和体温都显示在一个地方，有位置可以输入每个数值，还能快速看出每个数字是否在正常范围内。</v>
       </c>
       <c r="L361" t="str">
-        <v>[q_scene_037_001] 超时 180000ms</v>
+        <v/>
       </c>
     </row>
     <row r="362">
@@ -14156,19 +14156,19 @@
         <v>medium</v>
       </c>
       <c r="H362">
+        <v>46</v>
+      </c>
+      <c r="I362">
         <v>0</v>
       </c>
-      <c r="I362">
-        <v>546834</v>
-      </c>
       <c r="J362" t="str">
-        <v/>
+        <v>Make a weekly health score tracker for my phone that shows how my overall health score changes across the week, with each day's score listed clearly and a simple line chart so I can see at a glance whether my health is trending better or worse.</v>
       </c>
       <c r="K362" t="str">
-        <v/>
+        <v>手机周健康评分追踪器，显示整周的健康评分怎样变化，每天的评分清晰列出，还有个简单的折线图，这样一眼就能看出健康是在变好还是变差。</v>
       </c>
       <c r="L362" t="str">
-        <v>[q_scene_037_002] 超时 180000ms</v>
+        <v/>
       </c>
     </row>
     <row r="363">
@@ -14194,19 +14194,19 @@
         <v>medium</v>
       </c>
       <c r="H363">
+        <v>49</v>
+      </c>
+      <c r="I363">
         <v>0</v>
       </c>
-      <c r="I363">
-        <v>546871</v>
-      </c>
       <c r="J363" t="str">
-        <v/>
+        <v>A medication tracker app for my phone that shows how consistently I've been taking each of my medications, with a calendar-style view where I can see which days I took them and which days I missed, plus a simple overall percentage so I know how well I'm keeping up.</v>
       </c>
       <c r="K363" t="str">
-        <v/>
+        <v>手机吃药追踪应用，显示我有多稳定地在吃每种药物，用日历风格的界面可以看出哪些天吃了、哪些天漏吃了，还有个简单的百分比，让我知道自己的吃药坚持度怎样。</v>
       </c>
       <c r="L363" t="str">
-        <v>[q_scene_037_003] 超时 180000ms</v>
+        <v/>
       </c>
     </row>
     <row r="364">
@@ -14232,19 +14232,19 @@
         <v>medium</v>
       </c>
       <c r="H364">
+        <v>51</v>
+      </c>
+      <c r="I364">
         <v>0</v>
       </c>
-      <c r="I364">
-        <v>546539</v>
-      </c>
       <c r="J364" t="str">
-        <v/>
+        <v>Make a weekly activity report for my phone that shows my step count and active minutes for each day of the week, with the daily numbers listed out clearly and a total at the bottom so I can see how active I've been overall and which days I moved the most.</v>
       </c>
       <c r="K364" t="str">
-        <v/>
+        <v>手机周活动报告，显示这一周每天的步数和活跃分钟数，每天的数字清楚地列出来，底部有个总数，这样我就能看出整周活动量有多大，还有哪些天活动最多。</v>
       </c>
       <c r="L364" t="str">
-        <v>[q_scene_037_004] 超时 180000ms</v>
+        <v/>
       </c>
     </row>
     <row r="365">
@@ -14270,19 +14270,19 @@
         <v>medium</v>
       </c>
       <c r="H365">
+        <v>50</v>
+      </c>
+      <c r="I365">
         <v>0</v>
       </c>
-      <c r="I365">
-        <v>545416</v>
-      </c>
       <c r="J365" t="str">
-        <v/>
+        <v>Need a sleep quality tracker for my phone that shows how well I've been sleeping each week, with a simple chart that plots my sleep quality score day by day so I can see trends over the past few weeks and quickly tell if things are getting better or worse.</v>
       </c>
       <c r="K365" t="str">
-        <v/>
+        <v>手机睡眠质量追踪器，显示我最近每周睡眠质量怎样，有个简单的图表逐天绘制睡眠质量评分，这样能看出过去几周的趋势，快速判断睡眠是在变好还是变差。</v>
       </c>
       <c r="L365" t="str">
-        <v>[q_scene_037_005] 超时 180000ms</v>
+        <v/>
       </c>
     </row>
     <row r="366">
